--- a/Ket_Qua_Phan_Tich_SO SÁNH PP - ĐTCS/Phân tích dữ liệu.xlsx
+++ b/Ket_Qua_Phan_Tich_SO SÁNH PP - ĐTCS/Phân tích dữ liệu.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hadung1085/Downloads/du-an-dung-chung/Ket_Qua_Phan_Tich_SO SÁNH PP - ĐTCS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc-008\Desktop\du-an-dung-chung\Ket_Qua_Phan_Tich_SO SÁNH PP - ĐTCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9604DE-C908-254C-B477-20F0D4B1F09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13060" yWindow="500" windowWidth="15740" windowHeight="15900" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13065" yWindow="495" windowWidth="15735" windowHeight="15900" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Khác biệt tuyệt đối (Abs)" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Passing_Bablok_Prediction!$A$1:$R$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Passing_Bablok_Regression!$A$1:$L$19</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1370,7 +1369,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1718,42 +1717,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AE19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="63" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="27" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="41.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="9" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="46" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="49.1640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="49.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="49.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="49.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1848,7 +1847,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -1943,7 +1942,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -2038,7 +2037,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -2133,7 +2132,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -2228,7 +2227,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -2323,7 +2322,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -2418,7 +2417,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -2513,7 +2512,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="9" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -2608,7 +2607,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -2703,7 +2702,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>154</v>
       </c>
@@ -2798,7 +2797,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>154</v>
       </c>
@@ -2893,7 +2892,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>154</v>
       </c>
@@ -2988,7 +2987,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>154</v>
       </c>
@@ -3083,7 +3082,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>154</v>
       </c>
@@ -3178,7 +3177,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>154</v>
       </c>
@@ -3273,7 +3272,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>154</v>
       </c>
@@ -3368,7 +3367,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="18" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>154</v>
       </c>
@@ -3463,7 +3462,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="19" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>154</v>
       </c>
@@ -3559,7 +3558,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE19" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:AE19">
     <filterColumn colId="0">
       <filters>
         <filter val="Filtered 6 Analytes"/>
@@ -3578,42 +3577,42 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AE13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="63" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="27" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="37.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="9" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="48.5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="49.1640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="49.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="48.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="49.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="49.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3708,7 +3707,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -3803,7 +3802,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -3898,7 +3897,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -3993,7 +3992,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -4088,7 +4087,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="6" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -4183,7 +4182,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -4278,7 +4277,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>154</v>
       </c>
@@ -4373,7 +4372,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>154</v>
       </c>
@@ -4468,7 +4467,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>154</v>
       </c>
@@ -4563,7 +4562,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>154</v>
       </c>
@@ -4658,7 +4657,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>154</v>
       </c>
@@ -4753,7 +4752,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:31" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>154</v>
       </c>
@@ -4849,7 +4848,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE13" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <autoFilter ref="A1:AE13">
     <filterColumn colId="0">
       <filters>
         <filter val="Filtered 6 Analytes"/>
@@ -4868,26 +4867,26 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DE2D753-3C55-FF4C-9625-7E2128762188}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:P29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="23.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="48.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="48.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="49.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="48.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="48.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="49.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
@@ -4916,7 +4915,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>32</v>
       </c>
@@ -4945,7 +4944,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="3" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>50</v>
       </c>
@@ -4974,7 +4973,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="4" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>62</v>
       </c>
@@ -5003,7 +5002,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
@@ -5050,7 +5049,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>68</v>
       </c>
@@ -5097,7 +5096,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>113</v>
       </c>
@@ -5144,7 +5143,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>130</v>
       </c>
@@ -5191,7 +5190,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>1</v>
       </c>
@@ -5226,7 +5225,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>68</v>
       </c>
@@ -5261,7 +5260,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>113</v>
       </c>
@@ -5296,7 +5295,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>130</v>
       </c>
@@ -5331,7 +5330,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>1</v>
       </c>
@@ -5378,7 +5377,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>68</v>
       </c>
@@ -5425,7 +5424,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>68</v>
       </c>
@@ -5472,7 +5471,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>68</v>
       </c>
@@ -5519,7 +5518,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>68</v>
       </c>
@@ -5566,7 +5565,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>113</v>
       </c>
@@ -5613,7 +5612,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>113</v>
       </c>
@@ -5660,7 +5659,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>113</v>
       </c>
@@ -5707,7 +5706,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>130</v>
       </c>
@@ -5754,7 +5753,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>130</v>
       </c>
@@ -5807,26 +5806,26 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:L19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="95.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="95.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5864,7 +5863,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -5902,7 +5901,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -5940,7 +5939,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -5978,7 +5977,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -6016,7 +6015,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -6054,7 +6053,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -6092,7 +6091,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -6130,7 +6129,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -6168,7 +6167,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -6206,7 +6205,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>154</v>
       </c>
@@ -6244,7 +6243,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>154</v>
       </c>
@@ -6282,7 +6281,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>154</v>
       </c>
@@ -6320,7 +6319,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>154</v>
       </c>
@@ -6358,7 +6357,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>154</v>
       </c>
@@ -6396,7 +6395,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>154</v>
       </c>
@@ -6434,7 +6433,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>154</v>
       </c>
@@ -6472,7 +6471,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>154</v>
       </c>
@@ -6510,7 +6509,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>154</v>
       </c>
@@ -6549,7 +6548,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L19" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <autoFilter ref="A1:L19">
     <filterColumn colId="0">
       <filters>
         <filter val="Filtered 6 Analytes"/>
@@ -6568,15 +6567,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:R19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6632,7 +6631,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -6688,7 +6687,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>31</v>
       </c>
@@ -6744,7 +6743,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -6800,7 +6799,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -6856,7 +6855,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -6912,7 +6911,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -6968,7 +6967,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>31</v>
       </c>
@@ -7024,7 +7023,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -7080,7 +7079,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -7136,7 +7135,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>154</v>
       </c>
@@ -7192,7 +7191,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>154</v>
       </c>
@@ -7248,7 +7247,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>154</v>
       </c>
@@ -7304,7 +7303,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>154</v>
       </c>
@@ -7360,7 +7359,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>154</v>
       </c>
@@ -7416,7 +7415,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>154</v>
       </c>
@@ -7472,7 +7471,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>154</v>
       </c>
@@ -7528,7 +7527,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>154</v>
       </c>
@@ -7584,7 +7583,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>154</v>
       </c>
@@ -7641,7 +7640,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R19" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <autoFilter ref="A1:R19">
     <filterColumn colId="0">
       <filters>
         <filter val="Filtered 6 Analytes"/>
